--- a/docs/d/123/inyear.xlsx
+++ b/docs/d/123/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 22-Sep-2026. Built 2026-09-23 09:04 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:13 PDT.</t>
         </is>
       </c>
     </row>
@@ -1325,7 +1325,7 @@
         <v>0</v>
       </c>
       <c r="X6" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y6" s="9" t="n">
         <v>0</v>
@@ -1563,7 +1563,7 @@
         </is>
       </c>
       <c r="E9" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F9" s="6" t="n">
         <v>10</v>
@@ -1618,8 +1618,8 @@
       <c r="T9" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U9" s="9" t="n">
-        <v>0</v>
+      <c r="U9" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V9" s="10" t="n">
         <v>4</v>
@@ -3260,7 +3260,7 @@
         <v>0</v>
       </c>
       <c r="X25" s="10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y25" s="9" t="n">
         <v>0</v>
@@ -3970,7 +3970,7 @@
         <v>1</v>
       </c>
       <c r="U32" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V32" s="10" t="n">
         <v>4</v>
@@ -5409,7 +5409,7 @@
         <v>0</v>
       </c>
       <c r="X46" s="10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y46" s="9" t="n">
         <v>0</v>
@@ -10514,8 +10514,8 @@
       <c r="W96" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X96" s="9" t="n">
-        <v>3</v>
+      <c r="X96" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="Y96" s="9" t="n">
         <v>0</v>
@@ -11125,7 +11125,7 @@
         <v>0</v>
       </c>
       <c r="X102" s="10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y102" s="9" t="n">
         <v>0</v>
@@ -11226,7 +11226,7 @@
         <v>0</v>
       </c>
       <c r="X103" s="10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y103" s="9" t="n">
         <v>0</v>
@@ -11844,7 +11844,7 @@
         <v>0</v>
       </c>
       <c r="X109" s="10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y109" s="9" t="n">
         <v>0</v>
@@ -11944,8 +11944,8 @@
       <c r="W110" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X110" s="9" t="n">
-        <v>3</v>
+      <c r="X110" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y110" s="9" t="n">
         <v>0</v>
@@ -12284,7 +12284,7 @@
         <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>

--- a/docs/d/123/inyear.xlsx
+++ b/docs/d/123/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:13 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:41 PDT.</t>
         </is>
       </c>
     </row>
@@ -1642,7 +1642,11 @@
       <c r="AB9" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC9" s="4" t="inlineStr"/>
+      <c r="AC9" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
@@ -2967,7 +2971,11 @@
       <c r="AB22" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC22" s="4" t="inlineStr"/>
+      <c r="AC22" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
@@ -3068,7 +3076,11 @@
       <c r="AB23" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC23" s="4" t="inlineStr"/>
+      <c r="AC23" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
@@ -3274,7 +3286,11 @@
       <c r="AB25" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC25" s="4" t="inlineStr"/>
+      <c r="AC25" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
@@ -3686,7 +3702,11 @@
       <c r="AB29" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC29" s="4" t="inlineStr"/>
+      <c r="AC29" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
@@ -4199,7 +4219,11 @@
       <c r="AB34" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC34" s="4" t="inlineStr"/>
+      <c r="AC34" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
@@ -4502,7 +4526,11 @@
       <c r="AB37" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC37" s="4" t="inlineStr"/>
+      <c r="AC37" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
@@ -4603,7 +4631,11 @@
       <c r="AB38" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC38" s="4" t="inlineStr"/>
+      <c r="AC38" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
@@ -5629,7 +5661,11 @@
       <c r="AB48" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC48" s="4" t="inlineStr"/>
+      <c r="AC48" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
@@ -6554,7 +6590,11 @@
       <c r="AB57" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC57" s="4" t="inlineStr"/>
+      <c r="AC57" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
@@ -6962,7 +7002,11 @@
       <c r="AB61" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC61" s="4" t="inlineStr"/>
+      <c r="AC61" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
@@ -7265,7 +7309,11 @@
       <c r="AB64" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC64" s="4" t="inlineStr"/>
+      <c r="AC64" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
@@ -7778,7 +7826,11 @@
       <c r="AB69" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC69" s="4" t="inlineStr"/>
+      <c r="AC69" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="4" t="inlineStr">
@@ -8186,7 +8238,11 @@
       <c r="AB73" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC73" s="4" t="inlineStr"/>
+      <c r="AC73" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="4" t="inlineStr">
@@ -8388,7 +8444,11 @@
       <c r="AB75" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC75" s="4" t="inlineStr"/>
+      <c r="AC75" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="4" t="inlineStr">
@@ -8590,7 +8650,11 @@
       <c r="AB77" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC77" s="4" t="inlineStr"/>
+      <c r="AC77" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="4" t="inlineStr">
@@ -8994,7 +9058,11 @@
       <c r="AB81" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC81" s="4" t="inlineStr"/>
+      <c r="AC81" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="4" t="inlineStr">

--- a/docs/d/123/inyear.xlsx
+++ b/docs/d/123/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:41 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 26-Sep-2026. Built 2026-09-27 12:40 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>280 days remain until 30 June 2027, when these scores become final.</t>
+          <t>276 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (99 days) - 11 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (95 days) - 11 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (158 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (154 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 43 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (185 days) - 39 clubs short</t>
         </is>
       </c>
     </row>
@@ -2933,7 +2933,7 @@
         </is>
       </c>
       <c r="P22" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q22" s="9" t="n">
         <v>0</v>
@@ -3728,7 +3728,7 @@
         </is>
       </c>
       <c r="E30" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F30" s="6" t="n">
         <v>10</v>
@@ -3783,8 +3783,8 @@
       <c r="T30" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U30" s="9" t="n">
-        <v>0</v>
+      <c r="U30" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V30" s="10" t="n">
         <v>4</v>
@@ -4140,7 +4140,7 @@
         </is>
       </c>
       <c r="E34" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F34" s="6" t="n">
         <v>10</v>
@@ -4183,8 +4183,8 @@
       <c r="P34" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="Q34" s="9" t="n">
-        <v>1</v>
+      <c r="Q34" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R34" s="9" t="n">
         <v>0</v>
@@ -7376,7 +7376,7 @@
         </is>
       </c>
       <c r="P65" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q65" s="9" t="n">
         <v>0</v>
@@ -7896,7 +7896,7 @@
         <v>0</v>
       </c>
       <c r="Q70" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R70" s="9" t="n">
         <v>0</v>
@@ -9084,7 +9084,7 @@
         </is>
       </c>
       <c r="E82" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F82" s="6" t="n">
         <v>10</v>
@@ -9154,8 +9154,8 @@
       <c r="Y82" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z82" s="9" t="n">
-        <v>0</v>
+      <c r="Z82" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA82" s="10" t="n">
         <v>1</v>
@@ -10720,7 +10720,7 @@
         </is>
       </c>
       <c r="E98" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F98" s="6" t="n">
         <v>10</v>
@@ -10790,8 +10790,8 @@
       <c r="Y98" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z98" s="9" t="n">
-        <v>0</v>
+      <c r="Z98" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA98" s="10" t="n">
         <v>1</v>
@@ -11431,7 +11431,7 @@
         </is>
       </c>
       <c r="E105" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F105" s="6" t="n">
         <v>10</v>
@@ -11501,8 +11501,8 @@
       <c r="Y105" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z105" s="9" t="n">
-        <v>0</v>
+      <c r="Z105" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA105" s="10" t="n">
         <v>1</v>
@@ -12150,7 +12150,7 @@
         </is>
       </c>
       <c r="E112" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F112" s="6" t="n">
         <v>10</v>
@@ -12220,8 +12220,8 @@
       <c r="Y112" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z112" s="9" t="n">
-        <v>0</v>
+      <c r="Z112" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA112" s="10" t="n">
         <v>1</v>
@@ -12517,7 +12517,7 @@
         <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -12847,7 +12847,7 @@
         <v>6</v>
       </c>
       <c r="D18" t="n">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -12946,7 +12946,7 @@
         <v>5</v>
       </c>
       <c r="D21" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -12979,7 +12979,7 @@
         <v>4</v>
       </c>
       <c r="D22" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -13012,7 +13012,7 @@
         <v>6</v>
       </c>
       <c r="D23" t="n">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>

--- a/docs/d/123/inyear.xlsx
+++ b/docs/d/123/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 26-Sep-2026. Built 2026-09-27 12:40 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 03-Oct-2026. Built 2026-10-04 12:22 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>276 days remain until 30 June 2027, when these scores become final.</t>
+          <t>269 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (95 days) - 11 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (88 days) - 11 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (154 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (147 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (185 days) - 39 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (178 days) - 24 clubs short</t>
         </is>
       </c>
     </row>
@@ -1155,7 +1155,7 @@
         </is>
       </c>
       <c r="E5" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F5" s="6" t="n">
         <v>10</v>
@@ -1225,8 +1225,8 @@
       <c r="Y5" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z5" s="9" t="n">
-        <v>0</v>
+      <c r="Z5" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA5" s="10" t="n">
         <v>1</v>
@@ -1260,7 +1260,7 @@
         </is>
       </c>
       <c r="E6" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F6" s="6" t="n">
         <v>10</v>
@@ -1315,8 +1315,8 @@
       <c r="T6" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U6" s="9" t="n">
-        <v>0</v>
+      <c r="U6" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V6" s="9" t="n">
         <v>0</v>
@@ -1712,7 +1712,7 @@
         <v>1</v>
       </c>
       <c r="Q10" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R10" s="9" t="n">
         <v>0</v>
@@ -2328,7 +2328,7 @@
         <v>0</v>
       </c>
       <c r="S16" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T16" s="10" t="n">
         <v>1</v>
@@ -2746,7 +2746,7 @@
         <v>1</v>
       </c>
       <c r="U20" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V20" s="9" t="n">
         <v>0</v>
@@ -3522,7 +3522,7 @@
         </is>
       </c>
       <c r="E28" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F28" s="6" t="n">
         <v>10</v>
@@ -3592,8 +3592,8 @@
       <c r="Y28" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z28" s="9" t="n">
-        <v>0</v>
+      <c r="Z28" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA28" s="10" t="n">
         <v>1</v>
@@ -4964,7 +4964,7 @@
         </is>
       </c>
       <c r="E42" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F42" s="6" t="n">
         <v>10</v>
@@ -5034,8 +5034,8 @@
       <c r="Y42" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z42" s="9" t="n">
-        <v>0</v>
+      <c r="Z42" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA42" s="10" t="n">
         <v>1</v>
@@ -5792,7 +5792,7 @@
         </is>
       </c>
       <c r="E50" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F50" s="6" t="n">
         <v>10</v>
@@ -5862,8 +5862,8 @@
       <c r="Y50" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z50" s="9" t="n">
-        <v>0</v>
+      <c r="Z50" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA50" s="10" t="n">
         <v>1</v>
@@ -5994,7 +5994,7 @@
         </is>
       </c>
       <c r="E52" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F52" s="6" t="n">
         <v>10</v>
@@ -6064,8 +6064,8 @@
       <c r="Y52" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z52" s="9" t="n">
-        <v>0</v>
+      <c r="Z52" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA52" s="10" t="n">
         <v>1</v>
@@ -6095,7 +6095,7 @@
         </is>
       </c>
       <c r="E53" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F53" s="6" t="n">
         <v>10</v>
@@ -6165,8 +6165,8 @@
       <c r="Y53" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z53" s="9" t="n">
-        <v>0</v>
+      <c r="Z53" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA53" s="10" t="n">
         <v>1</v>
@@ -6456,7 +6456,7 @@
         <v>0</v>
       </c>
       <c r="S56" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T56" s="9" t="n">
         <v>0</v>
@@ -6476,8 +6476,8 @@
       <c r="Y56" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z56" s="9" t="n">
-        <v>0</v>
+      <c r="Z56" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA56" s="9" t="n">
         <v>0</v>
@@ -7028,7 +7028,7 @@
         </is>
       </c>
       <c r="E62" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F62" s="6" t="n">
         <v>10</v>
@@ -7098,8 +7098,8 @@
       <c r="Y62" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z62" s="9" t="n">
-        <v>0</v>
+      <c r="Z62" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA62" s="10" t="n">
         <v>1</v>
@@ -7852,7 +7852,7 @@
         </is>
       </c>
       <c r="E70" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F70" s="6" t="n">
         <v>10</v>
@@ -7866,13 +7866,13 @@
         </is>
       </c>
       <c r="I70" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J70" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K70" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L70" s="7" t="inlineStr">
         <is>
@@ -7911,7 +7911,7 @@
         <v>0</v>
       </c>
       <c r="V70" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W70" s="9" t="n">
         <v>0</v>
@@ -7922,8 +7922,8 @@
       <c r="Y70" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z70" s="9" t="n">
-        <v>0</v>
+      <c r="Z70" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA70" s="10" t="n">
         <v>1</v>
@@ -8329,7 +8329,7 @@
         <v>0</v>
       </c>
       <c r="X74" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y74" s="9" t="n">
         <v>0</v>
@@ -8878,7 +8878,7 @@
         </is>
       </c>
       <c r="E80" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F80" s="6" t="n">
         <v>10</v>
@@ -8948,8 +8948,8 @@
       <c r="Y80" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z80" s="9" t="n">
-        <v>0</v>
+      <c r="Z80" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA80" s="10" t="n">
         <v>1</v>
@@ -9020,7 +9020,7 @@
         </is>
       </c>
       <c r="P81" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q81" s="9" t="n">
         <v>0</v>
@@ -9492,7 +9492,7 @@
         </is>
       </c>
       <c r="E86" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F86" s="6" t="n">
         <v>10</v>
@@ -9562,8 +9562,8 @@
       <c r="Y86" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z86" s="9" t="n">
-        <v>0</v>
+      <c r="Z86" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA86" s="10" t="n">
         <v>1</v>
@@ -10312,7 +10312,7 @@
         </is>
       </c>
       <c r="E94" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F94" s="6" t="n">
         <v>10</v>
@@ -10382,8 +10382,8 @@
       <c r="Y94" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z94" s="9" t="n">
-        <v>0</v>
+      <c r="Z94" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA94" s="10" t="n">
         <v>1</v>
@@ -10633,13 +10633,13 @@
         </is>
       </c>
       <c r="I97" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J97" s="4" t="n">
         <v>7</v>
       </c>
       <c r="K97" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L97" s="7" t="inlineStr">
         <is>
@@ -10678,7 +10678,7 @@
         <v>0</v>
       </c>
       <c r="V97" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W97" s="9" t="n">
         <v>0</v>
@@ -10926,7 +10926,7 @@
         </is>
       </c>
       <c r="E100" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F100" s="6" t="n">
         <v>10</v>
@@ -10996,8 +10996,8 @@
       <c r="Y100" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z100" s="9" t="n">
-        <v>0</v>
+      <c r="Z100" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA100" s="10" t="n">
         <v>1</v>
@@ -11027,7 +11027,7 @@
         </is>
       </c>
       <c r="E101" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F101" s="6" t="n">
         <v>10</v>
@@ -11079,8 +11079,8 @@
       <c r="S101" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T101" s="9" t="n">
-        <v>0</v>
+      <c r="T101" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U101" s="9" t="n">
         <v>0</v>
@@ -11097,8 +11097,8 @@
       <c r="Y101" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z101" s="9" t="n">
-        <v>0</v>
+      <c r="Z101" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA101" s="10" t="n">
         <v>1</v>
@@ -12049,7 +12049,7 @@
         </is>
       </c>
       <c r="E111" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F111" s="6" t="n">
         <v>10</v>
@@ -12063,13 +12063,13 @@
         </is>
       </c>
       <c r="I111" s="4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J111" s="4" t="n">
         <v>6</v>
       </c>
       <c r="K111" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L111" s="7" t="inlineStr">
         <is>
@@ -12108,7 +12108,7 @@
         <v>0</v>
       </c>
       <c r="V111" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W111" s="9" t="n">
         <v>0</v>
@@ -12119,8 +12119,8 @@
       <c r="Y111" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z111" s="9" t="n">
-        <v>0</v>
+      <c r="Z111" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA111" s="10" t="n">
         <v>1</v>
@@ -12319,7 +12319,7 @@
         <v>5</v>
       </c>
       <c r="D2" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -12484,7 +12484,7 @@
         <v>4</v>
       </c>
       <c r="D7" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -12583,7 +12583,7 @@
         <v>6</v>
       </c>
       <c r="D10" t="n">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -12616,7 +12616,7 @@
         <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -12649,7 +12649,7 @@
         <v>5</v>
       </c>
       <c r="D12" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -12715,7 +12715,7 @@
         <v>5</v>
       </c>
       <c r="D14" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -12748,7 +12748,7 @@
         <v>6</v>
       </c>
       <c r="D15" t="n">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -12814,7 +12814,7 @@
         <v>6</v>
       </c>
       <c r="D17" t="n">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -12847,7 +12847,7 @@
         <v>6</v>
       </c>
       <c r="D18" t="n">
-        <v>0.67</v>
+        <v>0.83</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -12913,7 +12913,7 @@
         <v>5</v>
       </c>
       <c r="D20" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -12946,7 +12946,7 @@
         <v>5</v>
       </c>
       <c r="D21" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -13012,7 +13012,7 @@
         <v>6</v>
       </c>
       <c r="D23" t="n">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>

--- a/docs/d/123/inyear.xlsx
+++ b/docs/d/123/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 03-Oct-2026. Built 2026-10-04 12:22 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:33 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>269 days remain until 30 June 2027, when these scores become final.</t>
+          <t>262 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (88 days) - 11 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (81 days) - 11 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (147 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (140 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (178 days) - 24 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (171 days) - 24 clubs short</t>
         </is>
       </c>
     </row>
@@ -862,13 +862,13 @@
         </is>
       </c>
       <c r="I2" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J2" s="4" t="n">
         <v>7</v>
       </c>
       <c r="K2" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L2" s="7" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>0</v>
       </c>
       <c r="V2" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W2" s="9" t="n">
         <v>0</v>
@@ -963,13 +963,13 @@
         </is>
       </c>
       <c r="I3" s="4" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J3" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L3" s="7" t="inlineStr">
         <is>
@@ -1064,17 +1064,17 @@
         </is>
       </c>
       <c r="I4" s="4" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="J4" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L4" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-5</v>
+      </c>
+      <c r="L4" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M4" s="8" t="n">
@@ -1109,7 +1109,7 @@
         <v>0</v>
       </c>
       <c r="V4" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W4" s="9" t="n">
         <v>0</v>
@@ -1169,17 +1169,17 @@
         </is>
       </c>
       <c r="I5" s="4" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="J5" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L5" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-9</v>
+      </c>
+      <c r="L5" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M5" s="8" t="n">
@@ -1214,7 +1214,7 @@
         <v>0</v>
       </c>
       <c r="V5" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W5" s="9" t="n">
         <v>0</v>
@@ -1274,13 +1274,13 @@
         </is>
       </c>
       <c r="I6" s="4" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="J6" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>0</v>
+        <v>-12</v>
       </c>
       <c r="L6" s="7" t="inlineStr">
         <is>
@@ -1375,13 +1375,13 @@
         </is>
       </c>
       <c r="I7" s="4" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="J7" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="L7" s="7" t="inlineStr">
         <is>
@@ -1476,13 +1476,13 @@
         </is>
       </c>
       <c r="I8" s="4" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="J8" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="L8" s="7" t="inlineStr">
         <is>
@@ -1577,13 +1577,13 @@
         </is>
       </c>
       <c r="I9" s="4" t="n">
-        <v>62</v>
+        <v>25</v>
       </c>
       <c r="J9" s="4" t="n">
         <v>58</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>4</v>
+        <v>-33</v>
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
@@ -1625,7 +1625,7 @@
         <v>4</v>
       </c>
       <c r="W9" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X9" s="10" t="n">
         <v>5</v>
@@ -1682,17 +1682,17 @@
         </is>
       </c>
       <c r="I10" s="4" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="J10" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L10" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-5</v>
+      </c>
+      <c r="L10" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M10" s="8" t="n">
@@ -1727,7 +1727,7 @@
         <v>0</v>
       </c>
       <c r="V10" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W10" s="9" t="n">
         <v>0</v>
@@ -1787,13 +1787,13 @@
         </is>
       </c>
       <c r="I11" s="4" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="J11" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="L11" s="7" t="inlineStr">
         <is>
@@ -1989,13 +1989,13 @@
         </is>
       </c>
       <c r="I13" s="4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J13" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L13" s="7" t="inlineStr">
         <is>
@@ -2090,13 +2090,13 @@
         </is>
       </c>
       <c r="I14" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J14" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L14" s="7" t="inlineStr">
         <is>
@@ -2191,13 +2191,13 @@
         </is>
       </c>
       <c r="I15" s="4" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J15" s="4" t="n">
         <v>28</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L15" s="4" t="inlineStr">
         <is>
@@ -2292,17 +2292,17 @@
         </is>
       </c>
       <c r="I16" s="4" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="J16" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-8</v>
+      </c>
+      <c r="L16" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M16" s="8" t="n">
@@ -2397,13 +2397,13 @@
         </is>
       </c>
       <c r="I17" s="4" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="J17" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L17" s="7" t="inlineStr">
         <is>
@@ -2498,17 +2498,17 @@
         </is>
       </c>
       <c r="I18" s="4" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="J18" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L18" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-11</v>
+      </c>
+      <c r="L18" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M18" s="8" t="n">
@@ -2603,13 +2603,13 @@
         </is>
       </c>
       <c r="I19" s="4" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="J19" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="L19" s="7" t="inlineStr">
         <is>
@@ -2704,13 +2704,13 @@
         </is>
       </c>
       <c r="I20" s="4" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="J20" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L20" s="7" t="inlineStr">
         <is>
@@ -2805,13 +2805,13 @@
         </is>
       </c>
       <c r="I21" s="4" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="J21" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>1</v>
+        <v>-7</v>
       </c>
       <c r="L21" s="7" t="inlineStr">
         <is>
@@ -2850,7 +2850,7 @@
         <v>0</v>
       </c>
       <c r="V21" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W21" s="9" t="n">
         <v>0</v>
@@ -2906,13 +2906,13 @@
         </is>
       </c>
       <c r="I22" s="4" t="n">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="J22" s="4" t="n">
         <v>30</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>4</v>
+        <v>-6</v>
       </c>
       <c r="L22" s="4" t="inlineStr">
         <is>
@@ -3011,13 +3011,13 @@
         </is>
       </c>
       <c r="I23" s="4" t="n">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="J23" s="4" t="n">
         <v>35</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>3</v>
+        <v>-4</v>
       </c>
       <c r="L23" s="4" t="inlineStr">
         <is>
@@ -3116,17 +3116,17 @@
         </is>
       </c>
       <c r="I24" s="4" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="J24" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L24" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-6</v>
+      </c>
+      <c r="L24" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M24" s="8" t="n">
@@ -3221,17 +3221,17 @@
         </is>
       </c>
       <c r="I25" s="4" t="n">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="J25" s="4" t="n">
         <v>30</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L25" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-17</v>
+      </c>
+      <c r="L25" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M25" s="8" t="n">
@@ -3326,13 +3326,13 @@
         </is>
       </c>
       <c r="I26" s="4" t="n">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="J26" s="4" t="n">
         <v>31</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>4</v>
+        <v>-4</v>
       </c>
       <c r="L26" s="4" t="inlineStr">
         <is>
@@ -3362,7 +3362,7 @@
         <v>0</v>
       </c>
       <c r="S26" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T26" s="9" t="n">
         <v>0</v>
@@ -3374,7 +3374,7 @@
         <v>4</v>
       </c>
       <c r="W26" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X26" s="10" t="n">
         <v>7</v>
@@ -3431,13 +3431,13 @@
         </is>
       </c>
       <c r="I27" s="4" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="J27" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="L27" s="7" t="inlineStr">
         <is>
@@ -3522,7 +3522,7 @@
         </is>
       </c>
       <c r="E28" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F28" s="6" t="n">
         <v>10</v>
@@ -3536,17 +3536,17 @@
         </is>
       </c>
       <c r="I28" s="4" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J28" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L28" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>3</v>
+      </c>
+      <c r="L28" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M28" s="8" t="n">
@@ -3580,8 +3580,8 @@
       <c r="U28" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V28" s="9" t="n">
-        <v>0</v>
+      <c r="V28" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W28" s="9" t="n">
         <v>0</v>
@@ -3637,17 +3637,17 @@
         </is>
       </c>
       <c r="I29" s="4" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="J29" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L29" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-9</v>
+      </c>
+      <c r="L29" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M29" s="8" t="n">
@@ -3742,13 +3742,13 @@
         </is>
       </c>
       <c r="I30" s="4" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="J30" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>4</v>
+        <v>-1</v>
       </c>
       <c r="L30" s="4" t="inlineStr">
         <is>
@@ -3847,13 +3847,13 @@
         </is>
       </c>
       <c r="I31" s="4" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="J31" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L31" s="7" t="inlineStr">
         <is>
@@ -3892,7 +3892,7 @@
         <v>0</v>
       </c>
       <c r="V31" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W31" s="9" t="n">
         <v>0</v>
@@ -3934,7 +3934,7 @@
         </is>
       </c>
       <c r="E32" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F32" s="6" t="n">
         <v>10</v>
@@ -3948,17 +3948,17 @@
         </is>
       </c>
       <c r="I32" s="4" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="J32" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="L32" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-5</v>
+      </c>
+      <c r="L32" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M32" s="8" t="n">
@@ -3995,8 +3995,8 @@
       <c r="V32" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W32" s="9" t="n">
-        <v>2</v>
+      <c r="W32" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X32" s="10" t="n">
         <v>4</v>
@@ -4053,13 +4053,13 @@
         </is>
       </c>
       <c r="I33" s="4" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="J33" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>1</v>
+        <v>-4</v>
       </c>
       <c r="L33" s="4" t="inlineStr">
         <is>
@@ -4154,13 +4154,13 @@
         </is>
       </c>
       <c r="I34" s="4" t="n">
-        <v>54</v>
+        <v>31</v>
       </c>
       <c r="J34" s="4" t="n">
         <v>50</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>4</v>
+        <v>-19</v>
       </c>
       <c r="L34" s="4" t="inlineStr">
         <is>
@@ -4202,7 +4202,7 @@
         <v>4</v>
       </c>
       <c r="W34" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X34" s="10" t="n">
         <v>7</v>
@@ -4259,13 +4259,13 @@
         </is>
       </c>
       <c r="I35" s="4" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J35" s="4" t="n">
         <v>7</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L35" s="7" t="inlineStr">
         <is>
@@ -4360,13 +4360,13 @@
         </is>
       </c>
       <c r="I36" s="4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J36" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K36" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L36" s="7" t="inlineStr">
         <is>
@@ -4461,13 +4461,13 @@
         </is>
       </c>
       <c r="I37" s="4" t="n">
-        <v>39</v>
+        <v>22</v>
       </c>
       <c r="J37" s="4" t="n">
         <v>35</v>
       </c>
       <c r="K37" s="4" t="n">
-        <v>4</v>
+        <v>-13</v>
       </c>
       <c r="L37" s="4" t="inlineStr">
         <is>
@@ -4566,13 +4566,13 @@
         </is>
       </c>
       <c r="I38" s="4" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="J38" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K38" s="4" t="n">
-        <v>1</v>
+        <v>-5</v>
       </c>
       <c r="L38" s="4" t="inlineStr">
         <is>
@@ -4671,13 +4671,13 @@
         </is>
       </c>
       <c r="I39" s="4" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="J39" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K39" s="4" t="n">
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="L39" s="7" t="inlineStr">
         <is>
@@ -4873,17 +4873,17 @@
         </is>
       </c>
       <c r="I41" s="4" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J41" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K41" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L41" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-4</v>
+      </c>
+      <c r="L41" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M41" s="8" t="n">
@@ -5079,17 +5079,17 @@
         </is>
       </c>
       <c r="I43" s="4" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="J43" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K43" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L43" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-8</v>
+      </c>
+      <c r="L43" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M43" s="8" t="n">
@@ -5106,7 +5106,7 @@
         </is>
       </c>
       <c r="P43" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q43" s="9" t="n">
         <v>0</v>
@@ -5124,7 +5124,7 @@
         <v>0</v>
       </c>
       <c r="V43" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W43" s="9" t="n">
         <v>0</v>
@@ -5285,17 +5285,17 @@
         </is>
       </c>
       <c r="I45" s="4" t="n">
-        <v>39</v>
+        <v>1</v>
       </c>
       <c r="J45" s="4" t="n">
         <v>38</v>
       </c>
       <c r="K45" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L45" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-37</v>
+      </c>
+      <c r="L45" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M45" s="8" t="n">
@@ -5330,7 +5330,7 @@
         <v>1</v>
       </c>
       <c r="V45" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W45" s="9" t="n">
         <v>0</v>
@@ -5390,13 +5390,13 @@
         </is>
       </c>
       <c r="I46" s="4" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="J46" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K46" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L46" s="7" t="inlineStr">
         <is>
@@ -5491,13 +5491,13 @@
         </is>
       </c>
       <c r="I47" s="4" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="J47" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K47" s="4" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="L47" s="4" t="inlineStr">
         <is>
@@ -5596,13 +5596,13 @@
         </is>
       </c>
       <c r="I48" s="4" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="J48" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K48" s="4" t="n">
-        <v>2</v>
+        <v>-5</v>
       </c>
       <c r="L48" s="4" t="inlineStr">
         <is>
@@ -5701,13 +5701,13 @@
         </is>
       </c>
       <c r="I49" s="4" t="n">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="J49" s="4" t="n">
         <v>35</v>
       </c>
       <c r="K49" s="4" t="n">
-        <v>0</v>
+        <v>-14</v>
       </c>
       <c r="L49" s="4" t="inlineStr">
         <is>
@@ -5806,17 +5806,17 @@
         </is>
       </c>
       <c r="I50" s="4" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="J50" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K50" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L50" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-6</v>
+      </c>
+      <c r="L50" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M50" s="8" t="n">
@@ -5851,7 +5851,7 @@
         <v>0</v>
       </c>
       <c r="V50" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W50" s="9" t="n">
         <v>0</v>
@@ -5907,13 +5907,13 @@
         </is>
       </c>
       <c r="I51" s="4" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="J51" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K51" s="4" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="L51" s="7" t="inlineStr">
         <is>
@@ -6008,13 +6008,13 @@
         </is>
       </c>
       <c r="I52" s="4" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J52" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K52" s="4" t="n">
-        <v>3</v>
+        <v>-2</v>
       </c>
       <c r="L52" s="7" t="inlineStr">
         <is>
@@ -6109,13 +6109,13 @@
         </is>
       </c>
       <c r="I53" s="4" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="J53" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K53" s="4" t="n">
-        <v>4</v>
+        <v>-3</v>
       </c>
       <c r="L53" s="7" t="inlineStr">
         <is>
@@ -6214,13 +6214,13 @@
         </is>
       </c>
       <c r="I54" s="4" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="J54" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K54" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L54" s="7" t="inlineStr">
         <is>
@@ -6315,17 +6315,17 @@
         </is>
       </c>
       <c r="I55" s="4" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="J55" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K55" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L55" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-9</v>
+      </c>
+      <c r="L55" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M55" s="8" t="n">
@@ -6406,7 +6406,7 @@
         </is>
       </c>
       <c r="E56" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F56" s="6" t="n">
         <v>10</v>
@@ -6420,13 +6420,13 @@
         </is>
       </c>
       <c r="I56" s="4" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J56" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K56" s="4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L56" s="4" t="inlineStr">
         <is>
@@ -6464,8 +6464,8 @@
       <c r="U56" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V56" s="9" t="n">
-        <v>0</v>
+      <c r="V56" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W56" s="9" t="n">
         <v>0</v>
@@ -6660,7 +6660,7 @@
         <v>0</v>
       </c>
       <c r="Q58" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R58" s="9" t="n">
         <v>0</v>
@@ -6731,17 +6731,17 @@
         </is>
       </c>
       <c r="I59" s="4" t="n">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="J59" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K59" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="L59" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-6</v>
+      </c>
+      <c r="L59" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M59" s="8" t="n">
@@ -6836,13 +6836,13 @@
         </is>
       </c>
       <c r="I60" s="4" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="J60" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K60" s="4" t="n">
-        <v>4</v>
+        <v>-2</v>
       </c>
       <c r="L60" s="4" t="inlineStr">
         <is>
@@ -6884,7 +6884,7 @@
         <v>4</v>
       </c>
       <c r="W60" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X60" s="10" t="n">
         <v>4</v>
@@ -6923,7 +6923,7 @@
         </is>
       </c>
       <c r="E61" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F61" s="6" t="n">
         <v>10</v>
@@ -6937,17 +6937,17 @@
         </is>
       </c>
       <c r="I61" s="4" t="n">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="J61" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K61" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L61" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-8</v>
+      </c>
+      <c r="L61" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M61" s="8" t="n">
@@ -6981,11 +6981,11 @@
       <c r="U61" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V61" s="9" t="n">
-        <v>2</v>
+      <c r="V61" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W61" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X61" s="10" t="n">
         <v>5</v>
@@ -7042,13 +7042,13 @@
         </is>
       </c>
       <c r="I62" s="4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J62" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K62" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L62" s="7" t="inlineStr">
         <is>
@@ -7143,13 +7143,13 @@
         </is>
       </c>
       <c r="I63" s="4" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="J63" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K63" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L63" s="7" t="inlineStr">
         <is>
@@ -7244,13 +7244,13 @@
         </is>
       </c>
       <c r="I64" s="4" t="n">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="J64" s="4" t="n">
         <v>37</v>
       </c>
       <c r="K64" s="4" t="n">
-        <v>4</v>
+        <v>-7</v>
       </c>
       <c r="L64" s="4" t="inlineStr">
         <is>
@@ -7292,7 +7292,7 @@
         <v>4</v>
       </c>
       <c r="W64" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X64" s="10" t="n">
         <v>6</v>
@@ -7335,7 +7335,7 @@
         </is>
       </c>
       <c r="E65" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F65" s="6" t="n">
         <v>10</v>
@@ -7349,13 +7349,13 @@
         </is>
       </c>
       <c r="I65" s="4" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="J65" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K65" s="4" t="n">
-        <v>3</v>
+        <v>-4</v>
       </c>
       <c r="L65" s="7" t="inlineStr">
         <is>
@@ -7393,8 +7393,8 @@
       <c r="U65" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V65" s="9" t="n">
-        <v>3</v>
+      <c r="V65" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W65" s="9" t="n">
         <v>0</v>
@@ -7440,7 +7440,7 @@
         </is>
       </c>
       <c r="E66" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F66" s="6" t="n">
         <v>10</v>
@@ -7454,13 +7454,13 @@
         </is>
       </c>
       <c r="I66" s="4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J66" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K66" s="4" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L66" s="7" t="inlineStr">
         <is>
@@ -7495,8 +7495,8 @@
       <c r="T66" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U66" s="9" t="n">
-        <v>0</v>
+      <c r="U66" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V66" s="9" t="n">
         <v>1</v>
@@ -7541,7 +7541,7 @@
         </is>
       </c>
       <c r="E67" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F67" s="6" t="n">
         <v>10</v>
@@ -7555,13 +7555,13 @@
         </is>
       </c>
       <c r="I67" s="4" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="J67" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K67" s="4" t="n">
-        <v>1</v>
+        <v>-4</v>
       </c>
       <c r="L67" s="4" t="inlineStr">
         <is>
@@ -7599,8 +7599,8 @@
       <c r="U67" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V67" s="9" t="n">
-        <v>1</v>
+      <c r="V67" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W67" s="9" t="n">
         <v>0</v>
@@ -7660,13 +7660,13 @@
         </is>
       </c>
       <c r="I68" s="4" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="J68" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K68" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L68" s="7" t="inlineStr">
         <is>
@@ -7705,7 +7705,7 @@
         <v>0</v>
       </c>
       <c r="V68" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W68" s="9" t="n">
         <v>0</v>
@@ -7761,13 +7761,13 @@
         </is>
       </c>
       <c r="I69" s="4" t="n">
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="J69" s="4" t="n">
         <v>40</v>
       </c>
       <c r="K69" s="4" t="n">
-        <v>4</v>
+        <v>-15</v>
       </c>
       <c r="L69" s="4" t="inlineStr">
         <is>
@@ -7809,7 +7809,7 @@
         <v>4</v>
       </c>
       <c r="W69" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X69" s="10" t="n">
         <v>7</v>
@@ -7866,13 +7866,13 @@
         </is>
       </c>
       <c r="I70" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J70" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K70" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L70" s="7" t="inlineStr">
         <is>
@@ -7967,17 +7967,17 @@
         </is>
       </c>
       <c r="I71" s="4" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="J71" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K71" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L71" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-7</v>
+      </c>
+      <c r="L71" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M71" s="8" t="n">
@@ -8012,7 +8012,7 @@
         <v>0</v>
       </c>
       <c r="V71" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W71" s="9" t="n">
         <v>0</v>
@@ -8072,13 +8072,13 @@
         </is>
       </c>
       <c r="I72" s="4" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J72" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K72" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L72" s="7" t="inlineStr">
         <is>
@@ -8173,13 +8173,13 @@
         </is>
       </c>
       <c r="I73" s="4" t="n">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="J73" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K73" s="4" t="n">
-        <v>5</v>
+        <v>-5</v>
       </c>
       <c r="L73" s="4" t="inlineStr">
         <is>
@@ -8278,13 +8278,13 @@
         </is>
       </c>
       <c r="I74" s="4" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="J74" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K74" s="4" t="n">
-        <v>3</v>
+        <v>-3</v>
       </c>
       <c r="L74" s="7" t="inlineStr">
         <is>
@@ -8379,13 +8379,13 @@
         </is>
       </c>
       <c r="I75" s="4" t="n">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="J75" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K75" s="4" t="n">
-        <v>5</v>
+        <v>-8</v>
       </c>
       <c r="L75" s="4" t="inlineStr">
         <is>
@@ -8470,7 +8470,7 @@
         </is>
       </c>
       <c r="E76" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F76" s="6" t="n">
         <v>10</v>
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="I76" s="4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J76" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K76" s="4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L76" s="4" t="inlineStr">
         <is>
@@ -8531,8 +8531,8 @@
       <c r="V76" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W76" s="9" t="n">
-        <v>2</v>
+      <c r="W76" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="X76" s="10" t="n">
         <v>5</v>
@@ -8585,13 +8585,13 @@
         </is>
       </c>
       <c r="I77" s="4" t="n">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="J77" s="4" t="n">
         <v>38</v>
       </c>
       <c r="K77" s="4" t="n">
-        <v>5</v>
+        <v>-4</v>
       </c>
       <c r="L77" s="4" t="inlineStr">
         <is>
@@ -8690,13 +8690,13 @@
         </is>
       </c>
       <c r="I78" s="4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J78" s="4" t="n">
         <v>5</v>
       </c>
       <c r="K78" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L78" s="7" t="inlineStr">
         <is>
@@ -8892,13 +8892,13 @@
         </is>
       </c>
       <c r="I80" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J80" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K80" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L80" s="7" t="inlineStr">
         <is>
@@ -8993,13 +8993,13 @@
         </is>
       </c>
       <c r="I81" s="4" t="n">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="J81" s="4" t="n">
         <v>35</v>
       </c>
       <c r="K81" s="4" t="n">
-        <v>5</v>
+        <v>-2</v>
       </c>
       <c r="L81" s="4" t="inlineStr">
         <is>
@@ -9098,13 +9098,13 @@
         </is>
       </c>
       <c r="I82" s="4" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="J82" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K82" s="4" t="n">
-        <v>1</v>
+        <v>-6</v>
       </c>
       <c r="L82" s="7" t="inlineStr">
         <is>
@@ -9199,13 +9199,13 @@
         </is>
       </c>
       <c r="I83" s="4" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="J83" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K83" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L83" s="7" t="inlineStr">
         <is>
@@ -9304,13 +9304,13 @@
         </is>
       </c>
       <c r="I84" s="4" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J84" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K84" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L84" s="7" t="inlineStr">
         <is>
@@ -9405,13 +9405,13 @@
         </is>
       </c>
       <c r="I85" s="4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J85" s="4" t="n">
         <v>6</v>
       </c>
       <c r="K85" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L85" s="7" t="inlineStr">
         <is>
@@ -9506,13 +9506,13 @@
         </is>
       </c>
       <c r="I86" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J86" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K86" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L86" s="7" t="inlineStr">
         <is>
@@ -9551,7 +9551,7 @@
         <v>0</v>
       </c>
       <c r="V86" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W86" s="9" t="n">
         <v>0</v>
@@ -9607,13 +9607,13 @@
         </is>
       </c>
       <c r="I87" s="4" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="J87" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K87" s="4" t="n">
-        <v>-8</v>
+        <v>-12</v>
       </c>
       <c r="L87" s="7" t="inlineStr">
         <is>
@@ -9652,7 +9652,7 @@
         <v>0</v>
       </c>
       <c r="V87" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W87" s="9" t="n">
         <v>0</v>
@@ -9708,13 +9708,13 @@
         </is>
       </c>
       <c r="I88" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J88" s="4" t="n">
         <v>3</v>
       </c>
       <c r="K88" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L88" s="7" t="inlineStr">
         <is>
@@ -9809,13 +9809,13 @@
         </is>
       </c>
       <c r="I89" s="4" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="J89" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K89" s="4" t="n">
-        <v>2</v>
+        <v>-3</v>
       </c>
       <c r="L89" s="4" t="inlineStr">
         <is>
@@ -9839,7 +9839,7 @@
         <v>1</v>
       </c>
       <c r="Q89" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R89" s="9" t="n">
         <v>0</v>
@@ -9900,7 +9900,7 @@
         </is>
       </c>
       <c r="E90" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F90" s="6" t="n">
         <v>10</v>
@@ -9914,17 +9914,17 @@
         </is>
       </c>
       <c r="I90" s="4" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="J90" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K90" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L90" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-2</v>
+      </c>
+      <c r="L90" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M90" s="8" t="n">
@@ -9944,7 +9944,7 @@
         <v>0</v>
       </c>
       <c r="Q90" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R90" s="9" t="n">
         <v>0</v>
@@ -9952,14 +9952,14 @@
       <c r="S90" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T90" s="9" t="n">
-        <v>0</v>
+      <c r="T90" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U90" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V90" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W90" s="9" t="n">
         <v>0</v>
@@ -10019,13 +10019,13 @@
         </is>
       </c>
       <c r="I91" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J91" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K91" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L91" s="7" t="inlineStr">
         <is>
@@ -10326,17 +10326,17 @@
         </is>
       </c>
       <c r="I94" s="4" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J94" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K94" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L94" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-2</v>
+      </c>
+      <c r="L94" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M94" s="8" t="n">
@@ -10431,13 +10431,13 @@
         </is>
       </c>
       <c r="I95" s="4" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="J95" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K95" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L95" s="7" t="inlineStr">
         <is>
@@ -10532,13 +10532,13 @@
         </is>
       </c>
       <c r="I96" s="4" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J96" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K96" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L96" s="7" t="inlineStr">
         <is>
@@ -10568,7 +10568,7 @@
         <v>0</v>
       </c>
       <c r="S96" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T96" s="9" t="n">
         <v>0</v>
@@ -10577,7 +10577,7 @@
         <v>0</v>
       </c>
       <c r="V96" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W96" s="9" t="n">
         <v>0</v>
@@ -10633,13 +10633,13 @@
         </is>
       </c>
       <c r="I97" s="4" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J97" s="4" t="n">
         <v>7</v>
       </c>
       <c r="K97" s="4" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L97" s="7" t="inlineStr">
         <is>
@@ -10779,7 +10779,7 @@
         <v>0</v>
       </c>
       <c r="V98" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W98" s="9" t="n">
         <v>0</v>
@@ -10835,13 +10835,13 @@
         </is>
       </c>
       <c r="I99" s="4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="J99" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K99" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L99" s="7" t="inlineStr">
         <is>
@@ -10940,13 +10940,13 @@
         </is>
       </c>
       <c r="I100" s="4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="J100" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K100" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L100" s="7" t="inlineStr">
         <is>
@@ -10985,7 +10985,7 @@
         <v>0</v>
       </c>
       <c r="V100" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W100" s="9" t="n">
         <v>0</v>
@@ -11041,13 +11041,13 @@
         </is>
       </c>
       <c r="I101" s="4" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="J101" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K101" s="4" t="n">
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="L101" s="7" t="inlineStr">
         <is>
@@ -11086,7 +11086,7 @@
         <v>0</v>
       </c>
       <c r="V101" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W101" s="9" t="n">
         <v>0</v>
@@ -11142,13 +11142,13 @@
         </is>
       </c>
       <c r="I102" s="4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J102" s="4" t="n">
         <v>7</v>
       </c>
       <c r="K102" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L102" s="7" t="inlineStr">
         <is>
@@ -11187,7 +11187,7 @@
         <v>0</v>
       </c>
       <c r="V102" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W102" s="9" t="n">
         <v>0</v>
@@ -11243,13 +11243,13 @@
         </is>
       </c>
       <c r="I103" s="4" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="J103" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K103" s="4" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="L103" s="7" t="inlineStr">
         <is>
@@ -11344,13 +11344,13 @@
         </is>
       </c>
       <c r="I104" s="4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J104" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K104" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L104" s="7" t="inlineStr">
         <is>
@@ -11445,13 +11445,13 @@
         </is>
       </c>
       <c r="I105" s="4" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="J105" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K105" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L105" s="4" t="inlineStr">
         <is>
@@ -11490,7 +11490,7 @@
         <v>0</v>
       </c>
       <c r="V105" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W105" s="9" t="n">
         <v>0</v>
@@ -11550,13 +11550,13 @@
         </is>
       </c>
       <c r="I106" s="4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J106" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K106" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L106" s="7" t="inlineStr">
         <is>
@@ -11756,13 +11756,13 @@
         </is>
       </c>
       <c r="I108" s="4" t="n">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="J108" s="4" t="n">
         <v>32</v>
       </c>
       <c r="K108" s="4" t="n">
-        <v>5</v>
+        <v>-9</v>
       </c>
       <c r="L108" s="4" t="inlineStr">
         <is>
@@ -11804,7 +11804,7 @@
         <v>4</v>
       </c>
       <c r="W108" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="X108" s="10" t="n">
         <v>7</v>
@@ -11861,13 +11861,13 @@
         </is>
       </c>
       <c r="I109" s="4" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J109" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K109" s="4" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="L109" s="7" t="inlineStr">
         <is>
@@ -11962,13 +11962,13 @@
         </is>
       </c>
       <c r="I110" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J110" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K110" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L110" s="7" t="inlineStr">
         <is>
@@ -12007,7 +12007,7 @@
         <v>0</v>
       </c>
       <c r="V110" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W110" s="9" t="n">
         <v>0</v>
@@ -12150,7 +12150,7 @@
         </is>
       </c>
       <c r="E112" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F112" s="6" t="n">
         <v>10</v>
@@ -12208,11 +12208,11 @@
       <c r="U112" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V112" s="9" t="n">
-        <v>1</v>
+      <c r="V112" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W112" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X112" s="10" t="n">
         <v>4</v>
@@ -12334,7 +12334,7 @@
         <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -12367,7 +12367,7 @@
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -12433,7 +12433,7 @@
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -12466,7 +12466,7 @@
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -12484,7 +12484,7 @@
         <v>4</v>
       </c>
       <c r="D7" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -12517,13 +12517,13 @@
         <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -12532,7 +12532,7 @@
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -12598,7 +12598,7 @@
         <v>1</v>
       </c>
       <c r="I10" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -12631,7 +12631,7 @@
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
@@ -12649,7 +12649,7 @@
         <v>5</v>
       </c>
       <c r="D12" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -12664,7 +12664,7 @@
         <v>1</v>
       </c>
       <c r="I12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -12697,7 +12697,7 @@
         <v>1</v>
       </c>
       <c r="I13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -12715,7 +12715,7 @@
         <v>5</v>
       </c>
       <c r="D14" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -12730,7 +12730,7 @@
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -12748,7 +12748,7 @@
         <v>6</v>
       </c>
       <c r="D15" t="n">
-        <v>1.33</v>
+        <v>1.67</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -12763,7 +12763,7 @@
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -12814,7 +12814,7 @@
         <v>6</v>
       </c>
       <c r="D17" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -12880,7 +12880,7 @@
         <v>5</v>
       </c>
       <c r="D19" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -12895,7 +12895,7 @@
         <v>1</v>
       </c>
       <c r="I19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -12928,7 +12928,7 @@
         <v>2</v>
       </c>
       <c r="I20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -13012,7 +13012,7 @@
         <v>6</v>
       </c>
       <c r="D23" t="n">
-        <v>0.67</v>
+        <v>0.83</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>

--- a/docs/d/123/inyear.xlsx
+++ b/docs/d/123/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:33 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:38 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/123/inyear.xlsx
+++ b/docs/d/123/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:38 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 10:56 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/123/inyear.xlsx
+++ b/docs/d/123/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 10:56 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 11:03 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/123/inyear.xlsx
+++ b/docs/d/123/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 11:03 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 13:06 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/123/inyear.xlsx
+++ b/docs/d/123/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 13:06 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 17-Oct-2026. Built 2026-10-18 11:32 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>262 days remain until 30 June 2027, when these scores become final.</t>
+          <t>255 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (81 days) - 11 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (74 days) - 11 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (140 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (133 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (171 days) - 24 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (164 days) - 24 clubs short</t>
         </is>
       </c>
     </row>
@@ -848,7 +848,7 @@
         </is>
       </c>
       <c r="E2" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F2" s="6" t="n">
         <v>10</v>
@@ -889,10 +889,10 @@
         </is>
       </c>
       <c r="P2" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q2" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="Q2" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R2" s="9" t="n">
         <v>0</v>
@@ -1196,7 +1196,7 @@
         </is>
       </c>
       <c r="P5" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q5" s="9" t="n">
         <v>0</v>
@@ -2528,7 +2528,7 @@
         <v>1</v>
       </c>
       <c r="Q18" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R18" s="9" t="n">
         <v>0</v>
@@ -3948,13 +3948,13 @@
         </is>
       </c>
       <c r="I32" s="4" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J32" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-5</v>
+        <v>-3</v>
       </c>
       <c r="L32" s="7" t="inlineStr">
         <is>
@@ -4140,7 +4140,7 @@
         </is>
       </c>
       <c r="E34" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F34" s="6" t="n">
         <v>10</v>
@@ -4154,13 +4154,13 @@
         </is>
       </c>
       <c r="I34" s="4" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="J34" s="4" t="n">
         <v>50</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-19</v>
+        <v>-16</v>
       </c>
       <c r="L34" s="4" t="inlineStr">
         <is>
@@ -4201,8 +4201,8 @@
       <c r="V34" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W34" s="9" t="n">
-        <v>3</v>
+      <c r="W34" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="X34" s="10" t="n">
         <v>7</v>
@@ -4447,7 +4447,7 @@
         </is>
       </c>
       <c r="E37" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F37" s="6" t="n">
         <v>10</v>
@@ -4461,13 +4461,13 @@
         </is>
       </c>
       <c r="I37" s="4" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="J37" s="4" t="n">
         <v>35</v>
       </c>
       <c r="K37" s="4" t="n">
-        <v>-13</v>
+        <v>-7</v>
       </c>
       <c r="L37" s="4" t="inlineStr">
         <is>
@@ -4508,8 +4508,8 @@
       <c r="V37" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W37" s="9" t="n">
-        <v>0</v>
+      <c r="W37" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X37" s="10" t="n">
         <v>7</v>
@@ -4552,7 +4552,7 @@
         </is>
       </c>
       <c r="E38" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F38" s="6" t="n">
         <v>10</v>
@@ -4592,8 +4592,8 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P38" s="9" t="n">
-        <v>2</v>
+      <c r="P38" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Q38" s="9" t="n">
         <v>0</v>
@@ -6406,7 +6406,7 @@
         </is>
       </c>
       <c r="E56" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F56" s="6" t="n">
         <v>10</v>
@@ -6420,13 +6420,13 @@
         </is>
       </c>
       <c r="I56" s="4" t="n">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="J56" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K56" s="4" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="L56" s="4" t="inlineStr">
         <is>
@@ -6467,8 +6467,8 @@
       <c r="V56" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W56" s="9" t="n">
-        <v>0</v>
+      <c r="W56" s="10" t="n">
+        <v>16</v>
       </c>
       <c r="X56" s="10" t="n">
         <v>4</v>
@@ -6525,13 +6525,13 @@
         </is>
       </c>
       <c r="I57" s="4" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J57" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K57" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L57" s="4" t="inlineStr">
         <is>
@@ -6570,7 +6570,7 @@
         <v>0</v>
       </c>
       <c r="V57" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W57" s="9" t="n">
         <v>0</v>
@@ -6731,13 +6731,13 @@
         </is>
       </c>
       <c r="I59" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J59" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K59" s="4" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="L59" s="7" t="inlineStr">
         <is>
@@ -7143,13 +7143,13 @@
         </is>
       </c>
       <c r="I63" s="4" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J63" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K63" s="4" t="n">
-        <v>-4</v>
+        <v>-2</v>
       </c>
       <c r="L63" s="7" t="inlineStr">
         <is>
@@ -7230,7 +7230,7 @@
         </is>
       </c>
       <c r="E64" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F64" s="6" t="n">
         <v>10</v>
@@ -7244,13 +7244,13 @@
         </is>
       </c>
       <c r="I64" s="4" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="J64" s="4" t="n">
         <v>37</v>
       </c>
       <c r="K64" s="4" t="n">
-        <v>-7</v>
+        <v>-4</v>
       </c>
       <c r="L64" s="4" t="inlineStr">
         <is>
@@ -7282,8 +7282,8 @@
       <c r="S64" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T64" s="9" t="n">
-        <v>0</v>
+      <c r="T64" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U64" s="9" t="n">
         <v>0</v>
@@ -7291,8 +7291,8 @@
       <c r="V64" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W64" s="9" t="n">
-        <v>1</v>
+      <c r="W64" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X64" s="10" t="n">
         <v>6</v>
@@ -7555,13 +7555,13 @@
         </is>
       </c>
       <c r="I67" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J67" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K67" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L67" s="4" t="inlineStr">
         <is>
@@ -7660,13 +7660,13 @@
         </is>
       </c>
       <c r="I68" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J68" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K68" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L68" s="7" t="inlineStr">
         <is>
@@ -7705,7 +7705,7 @@
         <v>0</v>
       </c>
       <c r="V68" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W68" s="9" t="n">
         <v>0</v>
@@ -7747,7 +7747,7 @@
         </is>
       </c>
       <c r="E69" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F69" s="6" t="n">
         <v>10</v>
@@ -7761,13 +7761,13 @@
         </is>
       </c>
       <c r="I69" s="4" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J69" s="4" t="n">
         <v>40</v>
       </c>
       <c r="K69" s="4" t="n">
-        <v>-15</v>
+        <v>-13</v>
       </c>
       <c r="L69" s="4" t="inlineStr">
         <is>
@@ -7796,8 +7796,8 @@
       <c r="R69" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S69" s="9" t="n">
-        <v>1</v>
+      <c r="S69" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T69" s="9" t="n">
         <v>0</v>
@@ -7866,13 +7866,13 @@
         </is>
       </c>
       <c r="I70" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J70" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K70" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L70" s="7" t="inlineStr">
         <is>
@@ -7911,7 +7911,7 @@
         <v>0</v>
       </c>
       <c r="V70" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W70" s="9" t="n">
         <v>0</v>
@@ -8072,13 +8072,13 @@
         </is>
       </c>
       <c r="I72" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J72" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K72" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L72" s="7" t="inlineStr">
         <is>
@@ -8117,7 +8117,7 @@
         <v>0</v>
       </c>
       <c r="V72" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W72" s="9" t="n">
         <v>0</v>
@@ -8173,13 +8173,13 @@
         </is>
       </c>
       <c r="I73" s="4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J73" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K73" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L73" s="4" t="inlineStr">
         <is>
@@ -8221,7 +8221,7 @@
         <v>4</v>
       </c>
       <c r="W73" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X73" s="10" t="n">
         <v>7</v>
@@ -8365,7 +8365,7 @@
         </is>
       </c>
       <c r="E75" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F75" s="6" t="n">
         <v>10</v>
@@ -8379,13 +8379,13 @@
         </is>
       </c>
       <c r="I75" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J75" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K75" s="4" t="n">
-        <v>-8</v>
+        <v>-7</v>
       </c>
       <c r="L75" s="4" t="inlineStr">
         <is>
@@ -8408,8 +8408,8 @@
       <c r="P75" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="Q75" s="9" t="n">
-        <v>1</v>
+      <c r="Q75" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R75" s="9" t="n">
         <v>0</v>
@@ -8585,13 +8585,13 @@
         </is>
       </c>
       <c r="I77" s="4" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J77" s="4" t="n">
         <v>38</v>
       </c>
       <c r="K77" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L77" s="4" t="inlineStr">
         <is>
@@ -8633,7 +8633,7 @@
         <v>4</v>
       </c>
       <c r="W77" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X77" s="10" t="n">
         <v>7</v>
@@ -9914,13 +9914,13 @@
         </is>
       </c>
       <c r="I90" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J90" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K90" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L90" s="7" t="inlineStr">
         <is>
@@ -10532,13 +10532,13 @@
         </is>
       </c>
       <c r="I96" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J96" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K96" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L96" s="7" t="inlineStr">
         <is>
@@ -10940,13 +10940,13 @@
         </is>
       </c>
       <c r="I100" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J100" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K100" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L100" s="7" t="inlineStr">
         <is>
@@ -10985,7 +10985,7 @@
         <v>0</v>
       </c>
       <c r="V100" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W100" s="9" t="n">
         <v>0</v>
@@ -11270,7 +11270,7 @@
         </is>
       </c>
       <c r="P103" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q103" s="9" t="n">
         <v>0</v>
@@ -11756,13 +11756,13 @@
         </is>
       </c>
       <c r="I108" s="4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J108" s="4" t="n">
         <v>32</v>
       </c>
       <c r="K108" s="4" t="n">
-        <v>-9</v>
+        <v>-8</v>
       </c>
       <c r="L108" s="4" t="inlineStr">
         <is>
@@ -12319,7 +12319,7 @@
         <v>5</v>
       </c>
       <c r="D2" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -12517,7 +12517,7 @@
         <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="E8" t="n">
         <v>1</v>
@@ -12550,7 +12550,7 @@
         <v>6</v>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -12649,7 +12649,7 @@
         <v>5</v>
       </c>
       <c r="D12" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -12715,7 +12715,7 @@
         <v>5</v>
       </c>
       <c r="D14" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -12748,7 +12748,7 @@
         <v>6</v>
       </c>
       <c r="D15" t="n">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -12781,7 +12781,7 @@
         <v>4</v>
       </c>
       <c r="D16" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>

--- a/docs/d/123/inyear.xlsx
+++ b/docs/d/123/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 17-Oct-2026. Built 2026-10-18 11:32 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 24-Oct-2026. Built 2026-10-25 11:50 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>255 days remain until 30 June 2027, when these scores become final.</t>
+          <t>248 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (74 days) - 11 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (67 days) - 11 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (133 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (126 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (164 days) - 24 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (157 days) - 24 clubs short</t>
         </is>
       </c>
     </row>
@@ -1100,7 +1100,7 @@
         <v>0</v>
       </c>
       <c r="S4" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T4" s="9" t="n">
         <v>0</v>
@@ -1563,7 +1563,7 @@
         </is>
       </c>
       <c r="E9" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F9" s="6" t="n">
         <v>10</v>
@@ -1577,13 +1577,13 @@
         </is>
       </c>
       <c r="I9" s="4" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="J9" s="4" t="n">
         <v>58</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-33</v>
+        <v>-30</v>
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
@@ -1624,8 +1624,8 @@
       <c r="V9" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W9" s="9" t="n">
-        <v>1</v>
+      <c r="W9" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X9" s="10" t="n">
         <v>5</v>
@@ -3207,7 +3207,7 @@
         </is>
       </c>
       <c r="E25" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F25" s="6" t="n">
         <v>10</v>
@@ -3221,13 +3221,13 @@
         </is>
       </c>
       <c r="I25" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J25" s="4" t="n">
         <v>30</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-17</v>
+        <v>-16</v>
       </c>
       <c r="L25" s="7" t="inlineStr">
         <is>
@@ -3248,7 +3248,7 @@
         </is>
       </c>
       <c r="P25" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q25" s="9" t="n">
         <v>1</v>
@@ -3259,8 +3259,8 @@
       <c r="S25" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T25" s="9" t="n">
-        <v>0</v>
+      <c r="T25" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U25" s="9" t="n">
         <v>0</v>
@@ -3948,13 +3948,13 @@
         </is>
       </c>
       <c r="I32" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J32" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L32" s="7" t="inlineStr">
         <is>
@@ -4873,13 +4873,13 @@
         </is>
       </c>
       <c r="I41" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J41" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K41" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L41" s="7" t="inlineStr">
         <is>
@@ -5285,17 +5285,17 @@
         </is>
       </c>
       <c r="I45" s="4" t="n">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="J45" s="4" t="n">
         <v>38</v>
       </c>
       <c r="K45" s="4" t="n">
-        <v>-37</v>
-      </c>
-      <c r="L45" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-7</v>
+      </c>
+      <c r="L45" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M45" s="8" t="n">
@@ -5632,7 +5632,7 @@
         <v>0</v>
       </c>
       <c r="S48" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T48" s="9" t="n">
         <v>0</v>
@@ -6937,13 +6937,13 @@
         </is>
       </c>
       <c r="I61" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J61" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K61" s="4" t="n">
-        <v>-8</v>
+        <v>-7</v>
       </c>
       <c r="L61" s="7" t="inlineStr">
         <is>
@@ -7143,13 +7143,13 @@
         </is>
       </c>
       <c r="I63" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J63" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K63" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L63" s="7" t="inlineStr">
         <is>
@@ -7188,13 +7188,13 @@
         <v>0</v>
       </c>
       <c r="V63" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W63" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X63" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y63" s="9" t="n">
         <v>0</v>
@@ -7230,7 +7230,7 @@
         </is>
       </c>
       <c r="E64" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F64" s="6" t="n">
         <v>10</v>
@@ -7244,13 +7244,13 @@
         </is>
       </c>
       <c r="I64" s="4" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J64" s="4" t="n">
         <v>37</v>
       </c>
       <c r="K64" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L64" s="4" t="inlineStr">
         <is>
@@ -7274,7 +7274,7 @@
         <v>0</v>
       </c>
       <c r="Q64" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R64" s="9" t="n">
         <v>0</v>
@@ -7285,14 +7285,14 @@
       <c r="T64" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U64" s="9" t="n">
-        <v>0</v>
+      <c r="U64" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V64" s="10" t="n">
         <v>4</v>
       </c>
       <c r="W64" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X64" s="10" t="n">
         <v>6</v>
@@ -8072,13 +8072,13 @@
         </is>
       </c>
       <c r="I72" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J72" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K72" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L72" s="7" t="inlineStr">
         <is>
@@ -8117,7 +8117,7 @@
         <v>0</v>
       </c>
       <c r="V72" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W72" s="9" t="n">
         <v>0</v>
@@ -8264,7 +8264,7 @@
         </is>
       </c>
       <c r="E74" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F74" s="6" t="n">
         <v>10</v>
@@ -8316,8 +8316,8 @@
       <c r="S74" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T74" s="9" t="n">
-        <v>0</v>
+      <c r="T74" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U74" s="9" t="n">
         <v>0</v>
@@ -8365,7 +8365,7 @@
         </is>
       </c>
       <c r="E75" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F75" s="6" t="n">
         <v>10</v>
@@ -8417,8 +8417,8 @@
       <c r="S75" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T75" s="9" t="n">
-        <v>0</v>
+      <c r="T75" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U75" s="9" t="n">
         <v>0</v>
@@ -9533,7 +9533,7 @@
         </is>
       </c>
       <c r="P86" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q86" s="9" t="n">
         <v>0</v>
@@ -9809,13 +9809,13 @@
         </is>
       </c>
       <c r="I89" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J89" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K89" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L89" s="4" t="inlineStr">
         <is>
@@ -9854,7 +9854,7 @@
         <v>0</v>
       </c>
       <c r="V89" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W89" s="9" t="n">
         <v>0</v>
@@ -11742,7 +11742,7 @@
         </is>
       </c>
       <c r="E108" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F108" s="6" t="n">
         <v>10</v>
@@ -11756,13 +11756,13 @@
         </is>
       </c>
       <c r="I108" s="4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J108" s="4" t="n">
         <v>32</v>
       </c>
       <c r="K108" s="4" t="n">
-        <v>-8</v>
+        <v>-7</v>
       </c>
       <c r="L108" s="4" t="inlineStr">
         <is>
@@ -11803,8 +11803,8 @@
       <c r="V108" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W108" s="9" t="n">
-        <v>3</v>
+      <c r="W108" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X108" s="10" t="n">
         <v>7</v>
@@ -12352,13 +12352,13 @@
         <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -12451,7 +12451,7 @@
         <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -12598,7 +12598,7 @@
         <v>1</v>
       </c>
       <c r="I10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -12715,13 +12715,13 @@
         <v>5</v>
       </c>
       <c r="D14" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -12781,7 +12781,7 @@
         <v>4</v>
       </c>
       <c r="D16" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -13012,7 +13012,7 @@
         <v>6</v>
       </c>
       <c r="D23" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
